--- a/meeple_back/src/main/resources/game-element/telepathy.xlsx
+++ b/meeple_back/src/main/resources/game-element/telepathy.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12750"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15530" windowHeight="8670"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -636,7 +636,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -652,9 +652,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="168.75">
+    <row r="2" spans="1:4" ht="172.5">
       <c r="A2">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
@@ -666,9 +666,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="168.75">
+    <row r="3" spans="1:4" ht="172.5">
       <c r="A3">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B3" s="4">
         <v>2</v>
@@ -680,9 +680,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="180">
+    <row r="4" spans="1:4" ht="184">
       <c r="A4">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B4" s="4">
         <v>3</v>
@@ -694,9 +694,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="112.5">
+    <row r="5" spans="1:4" ht="126.5">
       <c r="A5">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B5" s="4">
         <v>4</v>
@@ -708,9 +708,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="135">
+    <row r="6" spans="1:4" ht="138">
       <c r="A6">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B6" s="4">
         <v>5</v>
@@ -722,9 +722,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="191.25">
+    <row r="7" spans="1:4" ht="195.5">
       <c r="A7">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B7" s="4">
         <v>6</v>
@@ -736,9 +736,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="123.75">
+    <row r="8" spans="1:4" ht="126.5">
       <c r="A8">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B8" s="4">
         <v>7</v>
@@ -750,9 +750,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="168.75">
+    <row r="9" spans="1:4" ht="172.5">
       <c r="A9">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B9" s="4">
         <v>8</v>
@@ -764,9 +764,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="168.75">
+    <row r="10" spans="1:4" ht="172.5">
       <c r="A10">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4">
         <v>9</v>
@@ -778,9 +778,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="270">
+    <row r="11" spans="1:4" ht="276">
       <c r="A11">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B11" s="4">
         <v>10</v>
@@ -792,9 +792,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="90">
+    <row r="12" spans="1:4" ht="92">
       <c r="A12">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B12" s="4">
         <v>11</v>
@@ -806,9 +806,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="146.25">
+    <row r="13" spans="1:4" ht="149.5">
       <c r="A13">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B13" s="4">
         <v>12</v>
@@ -820,9 +820,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="157.5">
+    <row r="14" spans="1:4" ht="161">
       <c r="A14">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B14" s="4">
         <v>13</v>
@@ -834,9 +834,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="135">
+    <row r="15" spans="1:4" ht="138">
       <c r="A15">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4">
         <v>14</v>
@@ -848,9 +848,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="168.75">
+    <row r="16" spans="1:4" ht="172.5">
       <c r="A16">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B16" s="4">
         <v>15</v>
@@ -862,9 +862,9 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="168.75">
+    <row r="17" spans="1:4" ht="195.5">
       <c r="A17">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B17" s="4">
         <v>16</v>
@@ -876,9 +876,9 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="112.5">
+    <row r="18" spans="1:4" ht="115">
       <c r="A18">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B18" s="4">
         <v>17</v>
@@ -890,9 +890,9 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="180">
+    <row r="19" spans="1:4" ht="184">
       <c r="A19">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B19" s="4">
         <v>18</v>
@@ -904,9 +904,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="101.25">
+    <row r="20" spans="1:4" ht="103.5">
       <c r="A20">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B20" s="4">
         <v>19</v>
@@ -918,9 +918,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="259.5" thickBot="1">
+    <row r="21" spans="1:4" ht="265" thickBot="1">
       <c r="A21">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="B21" s="6">
         <v>20</v>
@@ -932,9 +932,10 @@
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="17.25" thickTop="1"/>
+    <row r="22" spans="1:4" ht="17.5" thickTop="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>